--- a/Result/profitability/1813.xlsx
+++ b/Result/profitability/1813.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1350000000000001</v>
+        <v>-0.09625000000000004</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.99125</v>
+        <v>-10.62625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.62</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.03125000000000006</v>
+        <v>0.05374999999999994</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.411250000000002</v>
+        <v>0.40625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1037499999999999</v>
+        <v>0.1149999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>5.749999999999999</v>
+        <v>6.302499999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1412499999999999</v>
+        <v>0.2849999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>11.6975</v>
+        <v>13.13</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.31375</v>
+        <v>0.3124999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>19.03</v>
+        <v>21.2075</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.36125</v>
+        <v>0.385</v>
       </c>
       <c r="N7" t="n">
-        <v>26.5325</v>
+        <v>28.835</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.43875</v>
+        <v>0.4374999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>34.31875</v>
+        <v>34.9925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.57</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4549999999999999</v>
+        <v>0.455</v>
       </c>
       <c r="N10" t="n">
         <v>39.32375</v>
@@ -1772,7 +1772,7 @@
         <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>0.43125</v>
+        <v>0.4312499999999999</v>
       </c>
       <c r="N11" t="n">
         <v>38.6125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>74</v>
+      </c>
+      <c r="D75" t="n">
+        <v>77</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-30.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2000000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-18.02125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.009999999999999995</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.09090909090909083</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.5341922695738355</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.095238095238095</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.7091584158415842</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
